--- a/output/final/Divinity_of_Christ_300_Questions.xlsx
+++ b/output/final/Divinity_of_Christ_300_Questions.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1628,6 +1628,2214 @@
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>أي من الآيات التالية تصرح بوضوح: «في البدء كان الكلمة والكلمة كان عند الله وكان الكلمة الله»؟</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>يوحنا 1: 1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>يوحنا 3: 16</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>متى 1: 21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>لوقا 2: 1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>ما اللقب الذي أُطلق على السيد المسيح ويفيد أزليته ووجوده قبل كل الدهور؟</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ابن الإنسان</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>الكائن على الكل إلهاً مباركاً</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>الألف والياء (الأول والآخر)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>جميع ما سبق</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>قال السيد المسيح لليهود: «قبل أن يكون إبراهيم ____».</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>كنت أنا</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>أنا كائن</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>وُلدت أنا</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>عرفت</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>إبراز سلطة المسيح في غفران الخطايا يدل على لاهوته لأن:</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>غفران الخطايا سلطان لله وحده</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>الأنبياء كانوا يغفرون الخطايا</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>مغفرة الخطايا مجرد كلمة تشجيعية</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>ليس لها علاقة باللاهوت</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>قال السيد المسيح: «أنا والآب ____».</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>متوافقان</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>واحد</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>صديقان</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>متشابهان</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>معجزة إقامة لعازر أظهرت سلطان المسيح على:</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>الطبيعة</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>الموت والحياة</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>الشياطين</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>الأمراض الجلدية فقط</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>عندما سأل المسيح تلاميذه «من تقولون إني أنا؟» أجاب بطرس:</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>أنت إيليا</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>أنت يوحنا المعمدان</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>أنت هو المسيح ابن الله الحي</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>أنت نبي عظيم</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>أي معجزة أظهرت سلطان المسيح المباشر على عناصر الطبيعة والرياح؟</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>شفاء الأعمى</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>إبراء العرج</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>انتهار الرياح وإسكات البحر</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>تحويل الماء إلى خمر</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>قبول المسيح للسجود من الناس (مثل المولود أعمى والبرص) يدل على:</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>استحقاقه للعبادة والألوهية</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>مجرد احترام تشريفي</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>تواضعه</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>سلطانه السياسي</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>قال بولس الرسول عن المسيح: «الذي فيه يحل كل ____ اللاهوت جسدياً».</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>نور</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ملء</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>جزء</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>مجد</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>المعجزة الأولى التي صنعها السيد المسيح في قانا الجليل هي:</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>إشباع الخمسة آلاف</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>تحويل الماء إلى خمر</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>شفاء المفلوج</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>مشيه على الماء</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>صفة «غير المتغير» هي صفة إلهية ثبتت للمسيح في آية:</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>يسوع المسيح هو هو أمساً واليوم وإلى الأبد</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>الله محبة</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>أنا هو نور العالم</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>أنا هو الراعي الصالح</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>«كل شيء به كان وبغيره لم يكن شيء مما كان» تشهد للمسيح بصفته:</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>الفادي</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>الخالق</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>الديان</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>المشرّع</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>غفر المسيح للمفلوج خطاياه أولاً قبل شفائه لكي يثبت:</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>أن الجسد غير مهم</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>سلطانه الإلهي على غفران الخطايا</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>اعتراض الفريسيين</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>ضعفه</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>أي من الألقاب التالية أطلقه إشعياء النبي على المسيح في إشعياء 9: 6؟</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>عجيباً مشيراً إلهاً قديراً</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>أباً أبدياً رئيس السلام</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>أ و ب معاً</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>نبي الأمم</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>أظهر المسيح معرفته بما في قلوب وأفكار الناس، وهذه الصفة هي:</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>القدرة الكلية</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>علام الغيوب (فاحص القلوب)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>التواجد في كل مكان</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>القداسة</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>معجزة إشباع الخمسة آلاف خبزة وسمكتين هي معجزة:</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>شفاء</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>خلق وتكثير</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>إقامة موتى</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>طرد شياطين</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>أين وُلد السيد المسيح بحسب النبوة والمكتوب؟</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>الناصرة</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>بيت لحم أفراتة</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>أورشليم</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>أريحا</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>سهل</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>كيف أثبت البابا شنودة لاهوت المسيح من خلال قيامته من بين الأموات؟</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>لأنه قام بسلطانه الذاتي: «لي سلطان أن أضعها ولي سلطان أن آخذها»</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>لأن الملاك أقامه</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>لأن قيامته كانت رمزية</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>لأن الأنبياء أقاموه</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ما الفرق بين معجزات الأنبياء ومعجزات السيد المسيح من حيث أسلوب الممارسة؟</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>الأنبياء صنعوها باسمهم والمسيح باسم الآب</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>الأنبياء بصلاة وتضرع لله، أما المسيح فبسلطانه وأمره الشخصي</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>لا يوجد فرق</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>المسيح لم يصنع معجزات بيده</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>كيف يُفهم اللاهوت القبطي عبارة «الآب أعظم مني» (يوحنا 14: 28)؟</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>قيلت عن اللاهوت</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>قيلت في حالة إخلائه لذاته وتجسده من جهة الناسوت والتواضع</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>تعني أن المسيح مخلوق</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>تعني انفصال الأقانيم</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>عبارة «حينئذ يعطون قيصر ما لقيصر وما لله لله» أظهرت المسيح كـ:</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>تأثير سياسي</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>صاحب حكمة إلهية فائقة تفحص النيات</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>معلم قانوني فقط</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>معارض للرومان</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>ما الدليل على وجود المسيح في كل مكان (التواجد الكلي) أثناء وجوده الجسدي على الأرض؟</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>قوله لنيقوديموس: «ليس أحد صعد إلى السماء إلا الذي نزل من السماء ابن الإنسان الذي هو في السماء»</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>مشيه على الماء</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>صومه أربعين يوماً</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>دخوله الهيكل</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>رد المسيح على الفريسيين عندما قالوا «لماذا يتكلم هذا بتجاديف؟ من يقدر أن يغفر خطايا إلا الله وحده؟»:</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>اعتذر عن كلامه</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>أكد سلطانه بشفاء المفلوج آمراً: «قم واحمل سريرك»</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>قال لهم إن النبي يغفر</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>صمت ولم يجب</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>صفة «الديان» تثبت لاهوت المسيح لأن الديان يجب أن يكون:</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>عادلاً فقط</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>غير محدود، فاحصاً القلوب والأفكار ومجازياً كل واحد حسب أعماله</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ملكاً أرضياً</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>كاهناً أعظم</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>سلطة المسيح على الشياطين كانت تتميز بـ:</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>استخدام أساليب السحر</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>الأمر المباشر والخضوع المطلق من الشياطين واعترافهم بألوهيته</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>الصلاة الطويلة لطرد كل شيطان</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>الاستعانة بالملائكة</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>كيف تشهد ألقاب المسيح «الأول والآخر» و«البداية والنهاية» في سفر الرؤيا للاهوته؟</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>تثبت أنه أول المخلوقات</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>تثبت أزليته وأبديته، وهي ألقاب خاصة برب المجد وحده</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>تشير إلى بداية خدمته</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>تشير إلى موته على الصليب</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>في معجزة خلق عينين للمولود أعمى من الطين، يظهر لاهوت المسيح من حيث إنه:</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>أعاد صياغة المادة كما فعل الله عند خلق آدم من تراب الأرض</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>استخدم الدواء المناسب</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>دعا الله ليرسل ملائكة</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>أجرى عملية جراحية</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>ماذا يعني القول بأن السيد المسيح هو «صورة الله غير المنظور» (كولوسي 1: 15)؟</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>تشابه سطحي</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>البهاء والنعمة الإلهية الظاهرة فيه والجوهر الإلهي المكتفي بالناسوت</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>لوحة مرسومة</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>أنه مجرد ملاك</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>شهادة الآب للمسيح في التجلي والمعمودية «هذا هو ابني الحبيب الذي به سررت» تشير إلى:</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>البنوة العامة بالمكانة</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>البنوة الذاتية الأزلية الفريدة (الموجود في أحضان الآب)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>التبني</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>التكليف بالنبوة</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>في حواره مع السامرية، أظهر المسيح لاهوته عندما:</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>طلب أن يشرب ماء</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>كشف لها أسرار حياتها الخفية وتنبأ عن العبادة بالروح والحق</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>أخبرها بأنه غريب</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>استراح عند البئر</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>قال المسيح: «حيثما اجتمع اثنان أو ثلاثة باسمي فهناك أكون في وسطهم». هذا الوعد يستلزم صفة:</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>القدرة الكلية</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>التواجد في كل مكان وزمان في نفس الوقت (اللانهائية)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>الرحمة الفائقة</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>الحكمة</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>ما العلاقة بين كفارة المسيح ولاهوته بحسب كتاب البابا شنودة؟</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>الكفارة لا تحتاج للاهوت</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>بما أن الخطية موجهة ضد الله غير المحدود، وجب أن تكون الكفارة غير محدودة وقيمة الفادي غير محدودة، وهو الله المتجسد</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>الكفارة تمت بفضل أعماله الصالحة فقط</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>الموت كان للاهوت</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>كيف يرد البابا شنودة على الاعتراض المأخوذ من آية «وأما ذلك اليوم وتلك الساعة فلا يعلم بهما أحد ولا الملائكة... ولا الابن إلا الآب» (مرقس 13: 32)؟</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>الابن لا يعلم شيئاً إطلاقاً</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>عدم المعرفة منسوب للناسوت أو بمعنى «لا يعلنها لكم» لحكمته، بينما بلاهوته مذخر فيه كل كنوز الحكمة والمعرفة</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>النص محرف</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>الآية تعني أن الآب ليس إلهاً</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>ما هو التفسير اللاهوتي الدقيق لقول المسيح للشاب الغني: «لماذا تدعوني صالحاً؟ ليس أحد صالحاً إلا واحد وهو الله» (مرقس 10: 18)؟</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>المسيح ينفي عن نفسه الصلاح</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>المسيح يوجه الشاب ليدرك أنه إن كان يعترف بصلاحه المطلق فيجب أن يعترف بألوهيته</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>المسيح يرفض الألقاب</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>الشاب كان يمزح</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>يفند البابا شنودة بدعة أريوس باستخدام مفهوم «الكلمة» (اللوغوس)؛ كيف يثبت أزلية الابن منطقياً؟</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>الله كان بدون عقل أو كلمة في وقت من الأوقات ثم أوجده</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>بما أن الابن هو عقل الله الناطق أو كلمته، والله أزلي ولا يوجد وقت كان فيه بلا عقل، فالكلمة أزلي بأزلية الله</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>الكلمة حادث ومخلوق</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>اللوغوس كلمة فلسفية لا تعني الألوهية</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>رد البابا شنودة على من يستدلون بآية «بكر كل خليقة» (كولوسي 1: 15) لنفي ألوهية المسيح، موضحاً أن كلمة «بكر» هنا تعني:</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>أول مخلوق خلقه الله</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>أسبق في الوجود والمقام والرأس لجميع الخلائق وعلة وجودها، وليست تعني أول حادث</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>المولود أولاً في الزمان</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>الأصغر مقاماً</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>آية «أبي يعمل حتى الآن وأنا أعمل» (يوحنا 5: 17) أثارت غضب اليهود لأنهم فهموا منها أن المسيح:</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>يخالف السبت فقط</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>يجعل نفسه مساوياً لله في الجوهر والسلطان والعمل الإلهي</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>يرفض العمل الجسدي</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>يفضل العمل على الصلاة</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>كيف يشرح الفرق بين عبارة «حلول الروح القدس على الأنبياء» و«حلول ملء اللاهوت في المسيح»؟</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>حلول الأنبياء حلول أقنومي دائم، أما المسيح فحلول مؤقت</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>حلول الأنبياء موهبي جزئي، أما في المسيح فهو حلول جوهري أقنومي ذاتي غير منفصل</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>لا يوجد فرق جوهري</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>الأنبياء حل فيهم اللاهوت بأعمق</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>اعتراض البعض بقول المسيح على الصليب «إلهي إلهي لماذا تركتني»؛ يوضح الكتاب أنها:</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>انفصال لاهوته عن ناسوته</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>اقتباس للمزمور 22 ونطق بلسان البشرية النائبة المحملة بالخطية ليكمل عمل الفداء دون انفصال اللاهوت</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ضعف وشك في الله</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>إنكار للاهوته</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>ما معنى أن السيد المسيح هو «شارع» أو «واضع القانون» في الموعظة على الجبل: «سمعتم أنه قيل للقدماء... وأما أنا فأقول لكم»؟</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>ينسخ الشريعة القديمة كلياً</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>يمارس سلطانه الإلهي التشريعي كصاحب الناموس الأصلي ومكمل له</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ينقل أقوال الفريسيين</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>يتكلم باسم نبي جديد</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>عبارة «لتكونوا أبناء أبيكم الذي في السماوات» مقارنة بـ«ابن الله الوحيد» تظهر الفارق اللاهوتي بين:</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>بنوة العهد القديم والجديد</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>بنوة البشر بالإيمان والتبني والنعمة، وبنوة المسيح للآب بالطبيعة والجوهر والأقنوم</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>لا يوجد فرق بينهما</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>بنوة الملائكة وبنوة البشر</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>استناد البابا شنودة إلى قولي المسيح «أنا هو نور العالم» و«أنتم نور العالم» يوضح أن:</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>نور المسيح ونور التلاميذ متماثلان</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>المسيح النور الأصلي الذاتي الخالق، بينما التلاميذ يستمدون نورهم منه كعكس للقمر</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>التلاميذ أفضل نوراً</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>النور مجرد رمز عرضي</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>يفسر اللاهوت القبطي الآية «متى أُخضع له الكل فحينئذ الابن نفسه أيضاً سيخضع للذي أخضع له الكل» (1 كورنثوس 15: 28) على أنها:</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>خضوع للناسوت والكنيسة (جسده) الممثلة فيه للآب في نهاية الأزمنة لاستعلان ملكوت الله</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>تقليل من مرتبة اللاهوت</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>إنكار لمساواة الأقانيم</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>خضوع زمني انتهى</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>ما معنى قول القديس بولس: «عظيم هو سر التقوى: الله ظهر في الجسد» (1 تيموثاوس 3: 16)؟</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>أن الجسد خيال</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>إعلان أن الذات الإلهية اتحدت وتجسدت في شخص المسيح الحقيقي للحلول والفداء</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ظهور ملاك في صورة جسد</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>رمز لصفات الله</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>أي من العبارات التالية تعبر بدقة عن عدم انفصال اللاهوت عن الناسوت أثناء موت المسيح بالجسد؟</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>اللاهوت مات مع الناسوت</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>اللاهوت فارق الناسوت والروح معاً</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>اللاهوت لم يفارق الروح ولا الجسد لحظة واحدة ولا طرفة عين، وانفصلت الروح الإنسانية عن الجسد الإنساني وظل اللاهوت متحداً بكليهما</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>الناسوت تحول إلى لاهوت</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>في رد البابا شنودة على من يقولون إن المسيح دُعي «ابن الإنسان» فلا يكون إلهاً، أوضح أن لقب «ابن الإنسان»:</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>ينفي اللاهوت</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>يعبر عن تجسده وناسوته، واستخدمه المسيح للإشارة إلى مجده الإلهي وسلطانه كديان على السحاب</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>لقب أطلقه أعداؤه فقط</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>يعني أنه مجرد بشر عادي</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>فريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>الخصوصية الفائقة لمعجزة صعود المسيح إلى السماء تجسد لاهوته لأنها تمت:</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>بمركبة نارية مثل إيليا</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>بقدرته وسلطانه الذاتي صاعداً إلى السماء حيث كان كائناً بلاهوته</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>بمساعدة الملائكة وحملهم له</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>اختفاء تدريجي فقط</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>صعب وتفصيلي</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>فريد</t>
         </is>
